--- a/ig/improve-doc/ValueSet-JDV-J02-XdsHealthcareFacilityTypeCode-CISIS.xlsx
+++ b/ig/improve-doc/ValueSet-JDV-J02-XdsHealthcareFacilityTypeCode-CISIS.xlsx
@@ -9,13 +9,12 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
-    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="172">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20240726120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2024-07-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -531,147 +530,6 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R02-SecteurActivite/FHIR/TRE-R02-SecteurActivite</t>
-  </si>
-  <si>
-    <t>182</t>
-  </si>
-  <si>
-    <t>Service d'Éducation Spéciale et de Soins à Domicile</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>Institut Médico-Educatif (I.M.E.)</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>Institut Thérapeutique Éducatif et Pédagogique (I.T.E.P.)</t>
-  </si>
-  <si>
-    <t>188</t>
-  </si>
-  <si>
-    <t>Etablissement pour Enfants ou Adolescents Polyhandicapés</t>
-  </si>
-  <si>
-    <t>189</t>
-  </si>
-  <si>
-    <t>Centre Médico-Psycho-Pédagogique (C.M.P.P.)</t>
-  </si>
-  <si>
-    <t>192</t>
-  </si>
-  <si>
-    <t>Institut d'éducation motrice</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>Institut pour Déficients Visuels</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>Institut pour Déficients Auditifs</t>
-  </si>
-  <si>
-    <t>196</t>
-  </si>
-  <si>
-    <t>Institut d'Education Sensorielle Sourd-Aveugle</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>Service autonomie aide et soins (SAAS)</t>
-  </si>
-  <si>
-    <t>221</t>
-  </si>
-  <si>
-    <t>Bureau d'Aide Psychologique Universitaire (B.A.P.U.)</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>Centre d'Accueil Familial Spécialisé</t>
-  </si>
-  <si>
-    <t>255</t>
-  </si>
-  <si>
-    <t>Maison d'Accueil Spécialisée (M.A.S.)</t>
-  </si>
-  <si>
-    <t>354</t>
-  </si>
-  <si>
-    <t>Service de Soins Infirmiers A Domicile (S.S.I.A.D)</t>
-  </si>
-  <si>
-    <t>390</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Temporaire d'Enfants Handicapés</t>
-  </si>
-  <si>
-    <t>395</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Temporaire pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>396</t>
-  </si>
-  <si>
-    <t>Foyer Hébergement Enfants et Adolescents Handicapés</t>
-  </si>
-  <si>
-    <t>445</t>
-  </si>
-  <si>
-    <t>Service d'accompagnement médico-social adultes handicapés</t>
-  </si>
-  <si>
-    <t>446</t>
-  </si>
-  <si>
-    <t>Service d'Accompagnement à la Vie Sociale (S.A.V.S.)</t>
-  </si>
-  <si>
-    <t>448</t>
-  </si>
-  <si>
-    <t>Etab.Acc.Médicalisé en tout ou partie personnes handicapées</t>
-  </si>
-  <si>
-    <t>449</t>
-  </si>
-  <si>
-    <t>Etab.Accueil Non Médicalisé pour personnes handicapées</t>
-  </si>
-  <si>
-    <t>460</t>
-  </si>
-  <si>
-    <t>Service autonomie aide (SAA)</t>
-  </si>
-  <si>
-    <t>640</t>
-  </si>
-  <si>
-    <t>Service d'aide et d'accompagnement à domicile aux familles (SAADF)</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R66-CategorieEtablissement/FHIR/TRE-R66-CategorieEtablissement</t>
   </si>
 </sst>
 </file>
@@ -1565,226 +1423,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>218</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>